--- a/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
@@ -522,6 +522,9 @@
       <c r="A11" t="str">
         <v>2</v>
       </c>
+      <c r="C11" t="str">
+        <v>52_康蒂娜_undefined_Gerbera L._10/20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
@@ -523,7 +523,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>52_康蒂娜_undefined_Gerbera L._10/20stems</v>
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
@@ -525,6 +525,9 @@
       <c r="C11" t="str">
         <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -583,7 +586,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01555352010510200</v>
+        <v>01555352010510208</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -529,9 +529,89 @@
         <v>8</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>283_窒息_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>728_金边朱蕉_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -586,7 +666,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01555352010510208</v>
+        <v>0155535201051020851013810191270</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
@@ -608,6 +608,9 @@
       <c r="C21" t="str">
         <v>728_金边朱蕉_undefined_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -666,7 +669,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0155535201051020851013810191270</v>
+        <v>0155535201051020851013810191275</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -612,9 +612,36 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>4</v>
+      </c>
+      <c r="C23" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L24"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -669,7 +696,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0155535201051020851013810191275</v>
+        <v>0155535201051020851013810191275101010</v>
       </c>
     </row>
   </sheetData>
